--- a/data/trans_dic/IP16A09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,81</t>
+          <t>0,0; 11,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 13,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 8,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 9,78</t>
+          <t>2,1; 9,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,29</t>
+          <t>0,56; 5,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,29</t>
+          <t>0,53; 5,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,6; 8,04</t>
+          <t>1,69; 8,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,83</t>
+          <t>0,7; 5,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,88</t>
+          <t>1,56; 6,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,39</t>
+          <t>1,64; 5,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,39</t>
+          <t>0,89; 4,18</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,46</t>
+          <t>0,0; 11,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,15</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,1</t>
+          <t>1,83; 15,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,41</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,13; 10,12</t>
+          <t>1,12; 9,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 5,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
     </row>
@@ -1007,17 +1008,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 7,96</t>
+          <t>1,81; 7,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 4,15</t>
+          <t>0,61; 4,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,66</t>
+          <t>0,35; 3,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1027,27 +1028,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,6</t>
+          <t>1,38; 5,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,67</t>
+          <t>0,47; 4,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,02</t>
+          <t>1,75; 5,22</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,08</t>
+          <t>1,35; 4,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,14</t>
+          <t>0,72; 2,88</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2452</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3175</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3516</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2556</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2558</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5372</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7533</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4376</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1697; 7881</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>645; 6052</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>565; 5678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4459</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2090; 9932</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>686; 5817</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2630; 10122</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3910; 13363</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1818; 8508</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>517</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2684</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4950</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5496</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2923</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>647; 5479</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4820</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3093</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>5197</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3501</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2277</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8469</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9083</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5075</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2266; 9194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1138; 8671</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>567; 5130</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1293; 7274</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2640; 10605</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>703; 6388</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>4705; 14006</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5103; 15211</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2245; 8960</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Estudios-trans_dic.xlsx
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,12</t>
+          <t>0,0; 13,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,31</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,76</t>
+          <t>2,21; 10,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,24</t>
+          <t>0,54; 5,18</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,36</t>
+          <t>0,53; 4,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,05</t>
+          <t>1,59; 8,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,95</t>
+          <t>0,7; 5,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 6,01</t>
+          <t>1,55; 5,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,59</t>
+          <t>1,64; 5,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,18</t>
+          <t>0,9; 4,39</t>
         </is>
       </c>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,9</t>
+          <t>0,0; 13,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 11,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 15,59</t>
+          <t>1,81; 14,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,0; 9,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,48</t>
+          <t>1,11; 10,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 7,34</t>
+          <t>1,9; 7,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,64</t>
+          <t>0,66; 4,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,16</t>
+          <t>0,35; 3,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,08</t>
+          <t>0,9; 5,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,54</t>
+          <t>1,3; 5,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,31</t>
+          <t>0,48; 4,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,22</t>
+          <t>1,66; 5,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,02</t>
+          <t>1,29; 3,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,88</t>
+          <t>0,77; 3,18</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2452</t>
+          <t>0; 2949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3175</t>
+          <t>0; 3059</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 2445</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2556</t>
+          <t>0; 3102</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1697; 7881</t>
+          <t>1784; 8072</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>645; 6052</t>
+          <t>628; 5991</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>565; 5678</t>
+          <t>564; 5209</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4459</t>
+          <t>0; 4512</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2090; 9932</t>
+          <t>1963; 9897</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>686; 5817</t>
+          <t>684; 5496</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2630; 10122</t>
+          <t>2603; 9607</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3910; 13363</t>
+          <t>3909; 12979</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1818; 8508</t>
+          <t>1838; 8943</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2684</t>
+          <t>0; 2943</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4950</t>
+          <t>0; 5216</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644; 5496</t>
+          <t>638; 5248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,22 +1657,22 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 2923</t>
+          <t>0; 3534</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>647; 5479</t>
+          <t>640; 5911</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4820</t>
+          <t>0; 5676</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3093</t>
+          <t>0; 3529</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2266; 9194</t>
+          <t>2376; 9439</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1138; 8671</t>
+          <t>1233; 7573</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>567; 5130</t>
+          <t>570; 5852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1293; 7274</t>
+          <t>1291; 7287</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2640; 10605</t>
+          <t>2493; 10500</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>703; 6388</t>
+          <t>707; 7017</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4705; 14006</t>
+          <t>4458; 14038</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5103; 15211</t>
+          <t>4866; 14812</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2245; 8960</t>
+          <t>2391; 9879</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A09-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,42 +678,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 12,22</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 13,81</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,39</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,27 +735,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,06%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2,21%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 10,0</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,18</t>
+          <t>1,6; 8,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,92</t>
+          <t>0,71; 5,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>2,29; 9,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,02</t>
+          <t>0,56; 5,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,63</t>
+          <t>0,54; 5,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 5,71</t>
+          <t>1,61; 5,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,64; 5,43</t>
+          <t>1,63; 5,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 4,39</t>
+          <t>0,98; 4,39</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,62%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,06%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,62%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,05</t>
+          <t>1,81; 15,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,41</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 9,46</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 11,15</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1,81; 14,88</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,38</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,22</t>
+          <t>1,13; 10,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 4,02</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,87%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,4%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,53</t>
+          <t>0,9; 5,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,05</t>
+          <t>1,36; 5,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,6</t>
+          <t>0,48; 4,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,09</t>
+          <t>2,02; 7,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,48</t>
+          <t>0,68; 4,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,74</t>
+          <t>0,35; 3,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,23</t>
+          <t>1,68; 5,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,91</t>
+          <t>1,35; 4,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,18</t>
+          <t>0,74; 3,14</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
+          <t>Menores que consumieron medicamentos para los vómitos (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1306,42 +1306,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2949</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 2792</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3045</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3059</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2445</t>
+          <t>0; 2431</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3102</t>
+          <t>0; 3163</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1289</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4975</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4083</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2558</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2277</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1289</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4975</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1784; 8072</t>
+          <t>0; 4858</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>628; 5991</t>
+          <t>1974; 9925</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>564; 5209</t>
+          <t>692; 5696</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4512</t>
+          <t>1851; 7896</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1963; 9897</t>
+          <t>646; 6112</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>684; 5496</t>
+          <t>570; 5605</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2603; 9607</t>
+          <t>2714; 9893</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3909; 12979</t>
+          <t>3888; 12877</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1838; 8943</t>
+          <t>1990; 8940</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>517</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2943</t>
+          <t>639; 5327</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5216</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 3168</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2134</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5114</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>638; 5248</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3534</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>640; 5911</t>
+          <t>654; 5851</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5676</t>
+          <t>0; 4670</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3529</t>
+          <t>0; 3031</t>
         </is>
       </c>
     </row>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3272</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5582</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2799</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>5197</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3501</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2277</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3272</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5582</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2799</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2376; 9439</t>
+          <t>1288; 7270</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1233; 7573</t>
+          <t>2611; 10721</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570; 5852</t>
+          <t>705; 6921</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1291; 7287</t>
+          <t>2528; 9976</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2493; 10500</t>
+          <t>1267; 7769</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>707; 7017</t>
+          <t>571; 5948</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4458; 14038</t>
+          <t>4514; 13485</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4866; 14812</t>
+          <t>5106; 15444</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2391; 9879</t>
+          <t>2305; 9767</t>
         </is>
       </c>
     </row>
